--- a/E/UMKM.xlsx
+++ b/E/UMKM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="17">
   <si>
     <t/>
   </si>
@@ -50,6 +50,9 @@
   </si>
   <si>
     <t>109</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
   </si>
   <si>
     <t>20132122</t>
@@ -459,7 +462,7 @@
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="5" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -539,15 +542,15 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -556,10 +559,10 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/E/UMKM.xlsx
+++ b/E/UMKM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="17">
   <si>
     <t/>
   </si>
@@ -454,7 +454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -462,10 +462,11 @@
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="5" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -484,8 +485,14 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -501,11 +508,11 @@
       <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -521,11 +528,11 @@
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -541,11 +548,11 @@
       <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -561,7 +568,7 @@
       <c r="E5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>13</v>
       </c>
     </row>

--- a/E/UMKM.xlsx
+++ b/E/UMKM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="17">
   <si>
     <t/>
   </si>
@@ -454,7 +454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -462,11 +462,10 @@
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="5" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -485,14 +484,8 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>0</v>
-      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -508,11 +501,11 @@
       <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -528,11 +521,11 @@
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -548,11 +541,11 @@
       <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -568,7 +561,7 @@
       <c r="E5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>13</v>
       </c>
     </row>

--- a/E/UMKM.xlsx
+++ b/E/UMKM.xlsx
@@ -11,42 +11,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
   <si>
     <t/>
   </si>
   <si>
-    <t>20132119</t>
-  </si>
-  <si>
-    <t>CIOMY CNKI AYM PDS80</t>
+    <t>20132121</t>
+  </si>
+  <si>
+    <t>CIOMY KEJU PDS CUP75</t>
   </si>
   <si>
     <t>UMKM</t>
   </si>
   <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20132120</t>
-  </si>
-  <si>
-    <t>CIOMY CNKI KJU PDS80</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>20132121</t>
-  </si>
-  <si>
-    <t>CIOMY KEJU PDS CUP75</t>
   </si>
   <si>
     <t>109</t>
@@ -454,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -525,46 +504,6 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
